--- a/data/controles_results/dif_medias/controls_vars/difmedias_controles_baselines_fixed_2021_T3_2.xlsx
+++ b/data/controles_results/dif_medias/controls_vars/difmedias_controles_baselines_fixed_2021_T3_2.xlsx
@@ -57,10 +57,10 @@
     <t>N</t>
   </si>
   <si>
-    <t>71</t>
-  </si>
-  <si>
-    <t>70</t>
+    <t>56</t>
+  </si>
+  <si>
+    <t>55</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -72,127 +72,127 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>5.63e+05</t>
-  </si>
-  <si>
-    <t>(73693.023)</t>
-  </si>
-  <si>
-    <t>499.227</t>
-  </si>
-  <si>
-    <t>(35.010)</t>
-  </si>
-  <si>
-    <t>3.622</t>
+    <t>5.24e+05</t>
+  </si>
+  <si>
+    <t>(80953.804)</t>
+  </si>
+  <si>
+    <t>503.534</t>
+  </si>
+  <si>
+    <t>(38.331)</t>
+  </si>
+  <si>
+    <t>3.714</t>
+  </si>
+  <si>
+    <t>(0.049)</t>
+  </si>
+  <si>
+    <t>6.411</t>
+  </si>
+  <si>
+    <t>(1.336)</t>
+  </si>
+  <si>
+    <t>87.003</t>
+  </si>
+  <si>
+    <t>(0.512)</t>
+  </si>
+  <si>
+    <t>8.97e+05</t>
+  </si>
+  <si>
+    <t>(55836.359)</t>
+  </si>
+  <si>
+    <t>2.162</t>
+  </si>
+  <si>
+    <t>(0.135)</t>
+  </si>
+  <si>
+    <t>2.339</t>
+  </si>
+  <si>
+    <t>(0.404)</t>
+  </si>
+  <si>
+    <t>29.286</t>
+  </si>
+  <si>
+    <t>(4.490)</t>
+  </si>
+  <si>
+    <t>0.929</t>
+  </si>
+  <si>
+    <t>(0.035)</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> (2) </t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>6.98e+05</t>
+  </si>
+  <si>
+    <t>(1.00e+05)</t>
+  </si>
+  <si>
+    <t>482.463</t>
+  </si>
+  <si>
+    <t>(43.823)</t>
+  </si>
+  <si>
+    <t>3.335</t>
   </si>
   <si>
     <t>(0.048)</t>
   </si>
   <si>
-    <t>9.380</t>
-  </si>
-  <si>
-    <t>(1.838)</t>
-  </si>
-  <si>
-    <t>88.049</t>
-  </si>
-  <si>
-    <t>(0.488)</t>
-  </si>
-  <si>
-    <t>1.02e+06</t>
-  </si>
-  <si>
-    <t>(56925.327)</t>
-  </si>
-  <si>
-    <t>2.449</t>
-  </si>
-  <si>
-    <t>(0.136)</t>
-  </si>
-  <si>
-    <t>3.099</t>
-  </si>
-  <si>
-    <t>(0.450)</t>
-  </si>
-  <si>
-    <t>33.282</t>
-  </si>
-  <si>
-    <t>(3.805)</t>
-  </si>
-  <si>
-    <t>0.944</t>
-  </si>
-  <si>
-    <t>(0.028)</t>
-  </si>
-  <si>
-    <t>45</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> (2) </t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>6.94e+05</t>
-  </si>
-  <si>
-    <t>(1.22e+05)</t>
-  </si>
-  <si>
-    <t>482.235</t>
-  </si>
-  <si>
-    <t>(51.428)</t>
-  </si>
-  <si>
-    <t>3.354</t>
-  </si>
-  <si>
-    <t>(0.055)</t>
-  </si>
-  <si>
-    <t>26.511</t>
-  </si>
-  <si>
-    <t>(3.670)</t>
-  </si>
-  <si>
-    <t>91.363</t>
-  </si>
-  <si>
-    <t>(0.442)</t>
-  </si>
-  <si>
-    <t>1.35e+06</t>
-  </si>
-  <si>
-    <t>(66657.795)</t>
-  </si>
-  <si>
-    <t>3.302</t>
-  </si>
-  <si>
-    <t>(0.135)</t>
-  </si>
-  <si>
-    <t>6.111</t>
-  </si>
-  <si>
-    <t>(0.594)</t>
-  </si>
-  <si>
-    <t>42.867</t>
-  </si>
-  <si>
-    <t>(3.225)</t>
+    <t>25.000</t>
+  </si>
+  <si>
+    <t>(3.191)</t>
+  </si>
+  <si>
+    <t>91.511</t>
+  </si>
+  <si>
+    <t>(0.367)</t>
+  </si>
+  <si>
+    <t>1.38e+06</t>
+  </si>
+  <si>
+    <t>(57218.217)</t>
+  </si>
+  <si>
+    <t>3.352</t>
+  </si>
+  <si>
+    <t>(0.119)</t>
+  </si>
+  <si>
+    <t>6.067</t>
+  </si>
+  <si>
+    <t>(0.544)</t>
+  </si>
+  <si>
+    <t>44.200</t>
+  </si>
+  <si>
+    <t>(2.738)</t>
   </si>
   <si>
     <t>1.000</t>
@@ -216,34 +216,34 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>1.30e+05</t>
-  </si>
-  <si>
-    <t>-16.993</t>
-  </si>
-  <si>
-    <t>-0.268***</t>
-  </si>
-  <si>
-    <t>17.131***</t>
-  </si>
-  <si>
-    <t>3.314***</t>
-  </si>
-  <si>
-    <t>3.31e+05***</t>
-  </si>
-  <si>
-    <t>0.853***</t>
-  </si>
-  <si>
-    <t>3.013***</t>
-  </si>
-  <si>
-    <t>9.585*</t>
-  </si>
-  <si>
-    <t>0.056</t>
+    <t>1.74e+05</t>
+  </si>
+  <si>
+    <t>-21.071</t>
+  </si>
+  <si>
+    <t>-0.380***</t>
+  </si>
+  <si>
+    <t>18.589***</t>
+  </si>
+  <si>
+    <t>4.508***</t>
+  </si>
+  <si>
+    <t>4.82e+05***</t>
+  </si>
+  <si>
+    <t>1.190***</t>
+  </si>
+  <si>
+    <t>3.727***</t>
+  </si>
+  <si>
+    <t>14.914***</t>
+  </si>
+  <si>
+    <t>0.071**</t>
   </si>
 </sst>
 </file>

--- a/data/controles_results/dif_medias/controls_vars/difmedias_controles_baselines_fixed_2021_T3_2.xlsx
+++ b/data/controles_results/dif_medias/controls_vars/difmedias_controles_baselines_fixed_2021_T3_2.xlsx
@@ -57,10 +57,10 @@
     <t>N</t>
   </si>
   <si>
-    <t>56</t>
-  </si>
-  <si>
-    <t>55</t>
+    <t>71</t>
+  </si>
+  <si>
+    <t>70</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -72,127 +72,127 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>5.24e+05</t>
-  </si>
-  <si>
-    <t>(80953.804)</t>
-  </si>
-  <si>
-    <t>503.534</t>
-  </si>
-  <si>
-    <t>(38.331)</t>
-  </si>
-  <si>
-    <t>3.714</t>
-  </si>
-  <si>
-    <t>(0.049)</t>
-  </si>
-  <si>
-    <t>6.411</t>
-  </si>
-  <si>
-    <t>(1.336)</t>
-  </si>
-  <si>
-    <t>87.003</t>
-  </si>
-  <si>
-    <t>(0.512)</t>
-  </si>
-  <si>
-    <t>8.97e+05</t>
-  </si>
-  <si>
-    <t>(55836.359)</t>
-  </si>
-  <si>
-    <t>2.162</t>
+    <t>5.63e+05</t>
+  </si>
+  <si>
+    <t>(73693.023)</t>
+  </si>
+  <si>
+    <t>499.227</t>
+  </si>
+  <si>
+    <t>(35.010)</t>
+  </si>
+  <si>
+    <t>3.622</t>
+  </si>
+  <si>
+    <t>(0.048)</t>
+  </si>
+  <si>
+    <t>9.380</t>
+  </si>
+  <si>
+    <t>(1.838)</t>
+  </si>
+  <si>
+    <t>88.049</t>
+  </si>
+  <si>
+    <t>(0.488)</t>
+  </si>
+  <si>
+    <t>1.02e+06</t>
+  </si>
+  <si>
+    <t>(56925.327)</t>
+  </si>
+  <si>
+    <t>2.449</t>
+  </si>
+  <si>
+    <t>(0.136)</t>
+  </si>
+  <si>
+    <t>3.099</t>
+  </si>
+  <si>
+    <t>(0.450)</t>
+  </si>
+  <si>
+    <t>33.282</t>
+  </si>
+  <si>
+    <t>(3.805)</t>
+  </si>
+  <si>
+    <t>0.944</t>
+  </si>
+  <si>
+    <t>(0.028)</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> (2) </t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>6.94e+05</t>
+  </si>
+  <si>
+    <t>(1.22e+05)</t>
+  </si>
+  <si>
+    <t>482.235</t>
+  </si>
+  <si>
+    <t>(51.428)</t>
+  </si>
+  <si>
+    <t>3.354</t>
+  </si>
+  <si>
+    <t>(0.055)</t>
+  </si>
+  <si>
+    <t>26.511</t>
+  </si>
+  <si>
+    <t>(3.670)</t>
+  </si>
+  <si>
+    <t>91.363</t>
+  </si>
+  <si>
+    <t>(0.442)</t>
+  </si>
+  <si>
+    <t>1.35e+06</t>
+  </si>
+  <si>
+    <t>(66657.795)</t>
+  </si>
+  <si>
+    <t>3.302</t>
   </si>
   <si>
     <t>(0.135)</t>
   </si>
   <si>
-    <t>2.339</t>
-  </si>
-  <si>
-    <t>(0.404)</t>
-  </si>
-  <si>
-    <t>29.286</t>
-  </si>
-  <si>
-    <t>(4.490)</t>
-  </si>
-  <si>
-    <t>0.929</t>
-  </si>
-  <si>
-    <t>(0.035)</t>
-  </si>
-  <si>
-    <t>60</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> (2) </t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>6.98e+05</t>
-  </si>
-  <si>
-    <t>(1.00e+05)</t>
-  </si>
-  <si>
-    <t>482.463</t>
-  </si>
-  <si>
-    <t>(43.823)</t>
-  </si>
-  <si>
-    <t>3.335</t>
-  </si>
-  <si>
-    <t>(0.048)</t>
-  </si>
-  <si>
-    <t>25.000</t>
-  </si>
-  <si>
-    <t>(3.191)</t>
-  </si>
-  <si>
-    <t>91.511</t>
-  </si>
-  <si>
-    <t>(0.367)</t>
-  </si>
-  <si>
-    <t>1.38e+06</t>
-  </si>
-  <si>
-    <t>(57218.217)</t>
-  </si>
-  <si>
-    <t>3.352</t>
-  </si>
-  <si>
-    <t>(0.119)</t>
-  </si>
-  <si>
-    <t>6.067</t>
-  </si>
-  <si>
-    <t>(0.544)</t>
-  </si>
-  <si>
-    <t>44.200</t>
-  </si>
-  <si>
-    <t>(2.738)</t>
+    <t>6.111</t>
+  </si>
+  <si>
+    <t>(0.594)</t>
+  </si>
+  <si>
+    <t>42.867</t>
+  </si>
+  <si>
+    <t>(3.225)</t>
   </si>
   <si>
     <t>1.000</t>
@@ -216,34 +216,34 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>1.74e+05</t>
-  </si>
-  <si>
-    <t>-21.071</t>
-  </si>
-  <si>
-    <t>-0.380***</t>
-  </si>
-  <si>
-    <t>18.589***</t>
-  </si>
-  <si>
-    <t>4.508***</t>
-  </si>
-  <si>
-    <t>4.82e+05***</t>
-  </si>
-  <si>
-    <t>1.190***</t>
-  </si>
-  <si>
-    <t>3.727***</t>
-  </si>
-  <si>
-    <t>14.914***</t>
-  </si>
-  <si>
-    <t>0.071**</t>
+    <t>1.30e+05</t>
+  </si>
+  <si>
+    <t>-16.993</t>
+  </si>
+  <si>
+    <t>-0.268***</t>
+  </si>
+  <si>
+    <t>17.131***</t>
+  </si>
+  <si>
+    <t>3.314***</t>
+  </si>
+  <si>
+    <t>3.31e+05***</t>
+  </si>
+  <si>
+    <t>0.853***</t>
+  </si>
+  <si>
+    <t>3.013***</t>
+  </si>
+  <si>
+    <t>9.585*</t>
+  </si>
+  <si>
+    <t>0.056</t>
   </si>
 </sst>
 </file>
